--- a/PAMaap/app/archives/XLXS_IMPORT/ALIMENTADORES/INVENTARIO_INFRA_beta.xlsx
+++ b/PAMaap/app/archives/XLXS_IMPORT/ALIMENTADORES/INVENTARIO_INFRA_beta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XimenaVanegas\Pictures\autompython\AutoM_python\Excel\ARCHIVOS_ALIMENTADORES_INFRA_AD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlos.bedoya\Documents\Documentacion\Equipo Infra\Scripts Python\autompython\PAMaap\app\archives\XLXS_IMPORT\ALIMENTADORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B5D0AC-410E-40D9-9FBA-FE393E00E05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8009D781-C9E3-4320-B0E3-30297BF7A6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INFRA" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="560">
   <si>
     <t>NOMBRE SERVERS</t>
   </si>
@@ -1689,6 +1689,33 @@
   </si>
   <si>
     <t xml:space="preserve">PDN </t>
+  </si>
+  <si>
+    <t>SRSPP801</t>
+  </si>
+  <si>
+    <t>SRSPP802</t>
+  </si>
+  <si>
+    <t>SRSPP803</t>
+  </si>
+  <si>
+    <t>SRSPP804</t>
+  </si>
+  <si>
+    <t>P8</t>
+  </si>
+  <si>
+    <t>10.203.4.177</t>
+  </si>
+  <si>
+    <t>10.203.4.178</t>
+  </si>
+  <si>
+    <t>10.205.31.93</t>
+  </si>
+  <si>
+    <t>10.205.31.92</t>
   </si>
 </sst>
 </file>
@@ -1880,7 +1907,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1945,7 +1972,6 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -2316,25 +2342,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G214"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G218"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="14" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="56.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="56.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" customWidth="1"/>
+    <col min="15" max="15" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2357,7 +2383,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -2380,7 +2406,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -2403,7 +2429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -2426,7 +2452,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -2447,7 +2473,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
@@ -2458,7 +2484,7 @@
       <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -2468,7 +2494,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -2489,7 +2515,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>29</v>
       </c>
@@ -2510,7 +2536,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>32</v>
       </c>
@@ -2529,7 +2555,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
@@ -2550,7 +2576,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>38</v>
       </c>
@@ -2571,7 +2597,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
@@ -2590,7 +2616,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>44</v>
       </c>
@@ -2611,7 +2637,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>47</v>
       </c>
@@ -2632,7 +2658,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>50</v>
       </c>
@@ -2653,7 +2679,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>53</v>
       </c>
@@ -2674,7 +2700,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>56</v>
       </c>
@@ -2695,7 +2721,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>58</v>
       </c>
@@ -2716,7 +2742,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>62</v>
       </c>
@@ -2737,7 +2763,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>64</v>
       </c>
@@ -2758,7 +2784,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>68</v>
       </c>
@@ -2779,7 +2805,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>72</v>
       </c>
@@ -2800,7 +2826,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>75</v>
       </c>
@@ -2821,7 +2847,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>77</v>
       </c>
@@ -2842,7 +2868,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>80</v>
       </c>
@@ -2863,7 +2889,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>82</v>
       </c>
@@ -2882,7 +2908,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>86</v>
       </c>
@@ -2901,7 +2927,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>88</v>
       </c>
@@ -2920,7 +2946,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>90</v>
       </c>
@@ -2939,7 +2965,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>93</v>
       </c>
@@ -2958,7 +2984,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>95</v>
       </c>
@@ -2979,7 +3005,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>99</v>
       </c>
@@ -2998,7 +3024,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>101</v>
       </c>
@@ -3017,7 +3043,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>103</v>
       </c>
@@ -3036,7 +3062,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>105</v>
       </c>
@@ -3057,7 +3083,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>109</v>
       </c>
@@ -3076,7 +3102,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>112</v>
       </c>
@@ -3099,7 +3125,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>117</v>
       </c>
@@ -3122,7 +3148,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>120</v>
       </c>
@@ -3145,7 +3171,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>123</v>
       </c>
@@ -3168,7 +3194,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>126</v>
       </c>
@@ -3191,7 +3217,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>129</v>
       </c>
@@ -3214,7 +3240,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>132</v>
       </c>
@@ -3237,7 +3263,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>135</v>
       </c>
@@ -3260,7 +3286,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>138</v>
       </c>
@@ -3283,7 +3309,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>141</v>
       </c>
@@ -3306,7 +3332,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>144</v>
       </c>
@@ -3329,7 +3355,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>147</v>
       </c>
@@ -3352,7 +3378,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>150</v>
       </c>
@@ -3375,7 +3401,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>153</v>
       </c>
@@ -3396,7 +3422,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>156</v>
       </c>
@@ -3419,7 +3445,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>159</v>
       </c>
@@ -3442,7 +3468,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>161</v>
       </c>
@@ -3465,7 +3491,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>164</v>
       </c>
@@ -3488,7 +3514,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>167</v>
       </c>
@@ -3511,7 +3537,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>170</v>
       </c>
@@ -3534,7 +3560,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>173</v>
       </c>
@@ -3557,7 +3583,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>176</v>
       </c>
@@ -3580,7 +3606,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>179</v>
       </c>
@@ -3603,7 +3629,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>182</v>
       </c>
@@ -3626,7 +3652,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>185</v>
       </c>
@@ -3649,7 +3675,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>188</v>
       </c>
@@ -3672,7 +3698,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>191</v>
       </c>
@@ -3693,7 +3719,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>194</v>
       </c>
@@ -3716,7 +3742,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>197</v>
       </c>
@@ -3739,7 +3765,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>200</v>
       </c>
@@ -3762,7 +3788,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>203</v>
       </c>
@@ -3783,7 +3809,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>206</v>
       </c>
@@ -3806,7 +3832,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>209</v>
       </c>
@@ -3827,7 +3853,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>212</v>
       </c>
@@ -3850,7 +3876,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>215</v>
       </c>
@@ -3871,7 +3897,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>218</v>
       </c>
@@ -3894,7 +3920,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>221</v>
       </c>
@@ -3917,7 +3943,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>224</v>
       </c>
@@ -3940,7 +3966,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>227</v>
       </c>
@@ -3963,7 +3989,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>230</v>
       </c>
@@ -3984,7 +4010,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>233</v>
       </c>
@@ -4005,7 +4031,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>236</v>
       </c>
@@ -4028,7 +4054,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>239</v>
       </c>
@@ -4049,7 +4075,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>242</v>
       </c>
@@ -4072,7 +4098,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>245</v>
       </c>
@@ -4095,7 +4121,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>248</v>
       </c>
@@ -4118,7 +4144,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>251</v>
       </c>
@@ -4141,7 +4167,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>254</v>
       </c>
@@ -4164,7 +4190,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>256</v>
       </c>
@@ -4187,7 +4213,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>258</v>
       </c>
@@ -4210,7 +4236,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>260</v>
       </c>
@@ -4233,7 +4259,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>262</v>
       </c>
@@ -4256,7 +4282,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>264</v>
       </c>
@@ -4279,7 +4305,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>266</v>
       </c>
@@ -4302,7 +4328,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>268</v>
       </c>
@@ -4325,7 +4351,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>270</v>
       </c>
@@ -4348,7 +4374,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>272</v>
       </c>
@@ -4371,7 +4397,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>274</v>
       </c>
@@ -4394,7 +4420,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>276</v>
       </c>
@@ -4417,7 +4443,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>278</v>
       </c>
@@ -4440,7 +4466,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>280</v>
       </c>
@@ -4463,7 +4489,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>282</v>
       </c>
@@ -4486,7 +4512,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>284</v>
       </c>
@@ -4509,7 +4535,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>286</v>
       </c>
@@ -4532,7 +4558,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>288</v>
       </c>
@@ -4555,7 +4581,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>290</v>
       </c>
@@ -4578,7 +4604,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>292</v>
       </c>
@@ -4601,7 +4627,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>294</v>
       </c>
@@ -4624,7 +4650,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>296</v>
       </c>
@@ -4647,7 +4673,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>298</v>
       </c>
@@ -4670,7 +4696,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>300</v>
       </c>
@@ -4693,7 +4719,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>302</v>
       </c>
@@ -4716,7 +4742,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>304</v>
       </c>
@@ -4739,7 +4765,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>306</v>
       </c>
@@ -4760,7 +4786,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>308</v>
       </c>
@@ -4783,7 +4809,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>310</v>
       </c>
@@ -4806,7 +4832,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>312</v>
       </c>
@@ -4829,7 +4855,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>314</v>
       </c>
@@ -4850,7 +4876,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>316</v>
       </c>
@@ -4873,7 +4899,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>318</v>
       </c>
@@ -4896,7 +4922,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>320</v>
       </c>
@@ -4919,7 +4945,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>322</v>
       </c>
@@ -4942,7 +4968,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>324</v>
       </c>
@@ -4965,7 +4991,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>326</v>
       </c>
@@ -4988,7 +5014,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>328</v>
       </c>
@@ -5011,7 +5037,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>330</v>
       </c>
@@ -5034,7 +5060,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>332</v>
       </c>
@@ -5057,7 +5083,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>334</v>
       </c>
@@ -5080,7 +5106,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>336</v>
       </c>
@@ -5103,7 +5129,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>338</v>
       </c>
@@ -5126,7 +5152,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>340</v>
       </c>
@@ -5149,7 +5175,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>342</v>
       </c>
@@ -5172,7 +5198,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>344</v>
       </c>
@@ -5193,7 +5219,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>347</v>
       </c>
@@ -5216,7 +5242,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>349</v>
       </c>
@@ -5239,7 +5265,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>351</v>
       </c>
@@ -5256,7 +5282,7 @@
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>354</v>
       </c>
@@ -5273,7 +5299,7 @@
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>356</v>
       </c>
@@ -5290,7 +5316,7 @@
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>358</v>
       </c>
@@ -5311,7 +5337,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>362</v>
       </c>
@@ -5332,7 +5358,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>364</v>
       </c>
@@ -5353,7 +5379,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>366</v>
       </c>
@@ -5374,7 +5400,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>368</v>
       </c>
@@ -5395,7 +5421,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>370</v>
       </c>
@@ -5414,7 +5440,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>373</v>
       </c>
@@ -5429,7 +5455,7 @@
       <c r="F141" s="4"/>
       <c r="G141" s="4"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>374</v>
       </c>
@@ -5448,7 +5474,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>377</v>
       </c>
@@ -5467,7 +5493,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>379</v>
       </c>
@@ -5482,7 +5508,7 @@
       <c r="F144" s="4"/>
       <c r="G144" s="4"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>380</v>
       </c>
@@ -5497,7 +5523,7 @@
       <c r="F145" s="4"/>
       <c r="G145" s="4"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>382</v>
       </c>
@@ -5514,7 +5540,7 @@
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>384</v>
       </c>
@@ -5533,7 +5559,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>386</v>
       </c>
@@ -5552,7 +5578,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>387</v>
       </c>
@@ -5571,7 +5597,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>389</v>
       </c>
@@ -5586,7 +5612,7 @@
       <c r="F150" s="4"/>
       <c r="G150" s="4"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>390</v>
       </c>
@@ -5603,7 +5629,7 @@
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>392</v>
       </c>
@@ -5618,7 +5644,7 @@
       <c r="F152" s="4"/>
       <c r="G152" s="4"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>393</v>
       </c>
@@ -5635,7 +5661,7 @@
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>396</v>
       </c>
@@ -5654,7 +5680,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>399</v>
       </c>
@@ -5675,7 +5701,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>402</v>
       </c>
@@ -5696,7 +5722,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>406</v>
       </c>
@@ -5715,7 +5741,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>408</v>
       </c>
@@ -5736,7 +5762,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>411</v>
       </c>
@@ -5757,7 +5783,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>413</v>
       </c>
@@ -5778,7 +5804,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>416</v>
       </c>
@@ -5799,7 +5825,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>418</v>
       </c>
@@ -5820,7 +5846,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>420</v>
       </c>
@@ -5841,7 +5867,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>422</v>
       </c>
@@ -5862,7 +5888,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>424</v>
       </c>
@@ -5883,7 +5909,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>426</v>
       </c>
@@ -5904,7 +5930,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>428</v>
       </c>
@@ -5925,7 +5951,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>430</v>
       </c>
@@ -5946,7 +5972,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>432</v>
       </c>
@@ -5967,7 +5993,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="16" t="s">
         <v>435</v>
       </c>
@@ -5982,7 +6008,7 @@
       <c r="F170" s="17"/>
       <c r="G170" s="17"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="16" t="s">
         <v>437</v>
       </c>
@@ -5997,7 +6023,7 @@
       <c r="F171" s="17"/>
       <c r="G171" s="17"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>439</v>
       </c>
@@ -6018,7 +6044,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>442</v>
       </c>
@@ -6039,7 +6065,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>445</v>
       </c>
@@ -6060,7 +6086,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>447</v>
       </c>
@@ -6081,7 +6107,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>449</v>
       </c>
@@ -6102,7 +6128,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>451</v>
       </c>
@@ -6123,7 +6149,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>453</v>
       </c>
@@ -6144,7 +6170,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="16" t="s">
         <v>457</v>
       </c>
@@ -6159,7 +6185,7 @@
       <c r="F179" s="20"/>
       <c r="G179" s="17"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="18" t="s">
         <v>459</v>
       </c>
@@ -6178,7 +6204,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>462</v>
       </c>
@@ -6197,7 +6223,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>465</v>
       </c>
@@ -6216,7 +6242,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>468</v>
       </c>
@@ -6237,7 +6263,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="21" t="s">
         <v>471</v>
       </c>
@@ -6258,7 +6284,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="4" t="s">
         <v>473</v>
       </c>
@@ -6273,7 +6299,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>475</v>
       </c>
@@ -6292,7 +6318,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>479</v>
       </c>
@@ -6313,7 +6339,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>482</v>
       </c>
@@ -6332,7 +6358,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>485</v>
       </c>
@@ -6353,7 +6379,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>488</v>
       </c>
@@ -6374,7 +6400,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="26" t="s">
         <v>491</v>
       </c>
@@ -6387,7 +6413,7 @@
       <c r="F191" s="28"/>
       <c r="G191" s="28"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>492</v>
       </c>
@@ -6408,7 +6434,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>494</v>
       </c>
@@ -6429,7 +6455,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>496</v>
       </c>
@@ -6450,7 +6476,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>500</v>
       </c>
@@ -6471,7 +6497,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="30" t="s">
         <v>502</v>
       </c>
@@ -6490,7 +6516,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>504</v>
       </c>
@@ -6511,7 +6537,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>508</v>
       </c>
@@ -6532,7 +6558,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="31" t="s">
         <v>510</v>
       </c>
@@ -6553,7 +6579,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>512</v>
       </c>
@@ -6574,7 +6600,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>515</v>
       </c>
@@ -6595,7 +6621,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>517</v>
       </c>
@@ -6616,7 +6642,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
         <v>519</v>
       </c>
@@ -6631,7 +6657,7 @@
       <c r="F203" s="4"/>
       <c r="G203" s="4"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>521</v>
       </c>
@@ -6652,7 +6678,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="32" t="s">
         <v>523</v>
       </c>
@@ -6673,7 +6699,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="32" t="s">
         <v>525</v>
       </c>
@@ -6694,7 +6720,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>526</v>
       </c>
@@ -6715,7 +6741,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>529</v>
       </c>
@@ -6736,7 +6762,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>532</v>
       </c>
@@ -6757,7 +6783,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>536</v>
       </c>
@@ -6778,7 +6804,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>539</v>
       </c>
@@ -6799,7 +6825,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>542</v>
       </c>
@@ -6818,7 +6844,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>544</v>
       </c>
@@ -6839,7 +6865,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>547</v>
       </c>
@@ -6857,6 +6883,98 @@
         <v>550</v>
       </c>
       <c r="G214" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A215" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B215" s="11" t="s">
+        <v>556</v>
+      </c>
+      <c r="C215" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A216" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B216" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="C216" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A217" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B217" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="C217" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A218" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B218" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="C218" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="G218" s="2" t="s">
         <v>61</v>
       </c>
     </row>

--- a/PAMaap/app/archives/XLXS_IMPORT/ALIMENTADORES/INVENTARIO_INFRA_beta.xlsx
+++ b/PAMaap/app/archives/XLXS_IMPORT/ALIMENTADORES/INVENTARIO_INFRA_beta.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlos.bedoya\Documents\Documentacion\Equipo Infra\Scripts Python\autompython\PAMaap\app\archives\XLXS_IMPORT\ALIMENTADORES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\autompython\PAMaap\app\archives\XLXS_IMPORT\ALIMENTADORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8009D781-C9E3-4320-B0E3-30297BF7A6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020"/>
   </bookViews>
   <sheets>
     <sheet name="INFRA" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1721,8 +1720,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1909,7 +1908,6 @@
   </cellStyleXfs>
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1924,9 +1922,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1972,12 +1967,80 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+    <cellStyle name="Hyperlink" xfId="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFFF0000"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2043,6 +2106,22 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:G1048576" totalsRowShown="0" headerRowDxfId="1" headerRowBorderDxfId="4" tableBorderDxfId="5">
+  <autoFilter ref="A1:G1048576"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="NOMBRE SERVERS"/>
+    <tableColumn id="2" name="Direccion IP" dataDxfId="3"/>
+    <tableColumn id="3" name="CONEXION" dataDxfId="2"/>
+    <tableColumn id="4" name="DOLIENTE "/>
+    <tableColumn id="5" name="TIPO_SERVER"/>
+    <tableColumn id="6" name="AMBIENTE"/>
+    <tableColumn id="7" name="UBICACION"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2341,4664 +2420,4670 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G218"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" style="14" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="56.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.33203125" customWidth="1"/>
-    <col min="15" max="15" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="32" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="C5" s="9"/>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="C6" s="9"/>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="F6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="13">
         <v>10201212254</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="C7" s="9"/>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="C8" s="9"/>
+      <c r="D8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="F8" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="C9" s="9"/>
+      <c r="D9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="3" t="s">
+      <c r="F9" s="1"/>
+      <c r="G9" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="C10" s="9"/>
+      <c r="D10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="F10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="C11" s="9"/>
+      <c r="D11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="F11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:7">
+      <c r="A12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="C12" s="9"/>
+      <c r="D12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="3" t="s">
+      <c r="F12" s="1"/>
+      <c r="G12" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:7">
+      <c r="A13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="C13" s="9"/>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="5" t="s">
+      <c r="F13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:7">
+      <c r="A14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="C14" s="9"/>
+      <c r="D14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="F14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:7">
+      <c r="A15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="C15" s="9"/>
+      <c r="D15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="F15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:7">
+      <c r="A16" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="C16" s="9"/>
+      <c r="D16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="F16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:7">
+      <c r="A17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="13">
         <v>10200122251</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="C17" s="9"/>
+      <c r="D17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="F17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:7">
+      <c r="A18" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="C18" s="9"/>
+      <c r="D18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="F18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:7">
+      <c r="A19" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="C19" s="9"/>
+      <c r="D19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="F19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:7">
+      <c r="A20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="C20" s="9"/>
+      <c r="D20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="F20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:7">
+      <c r="A21" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="C21" s="9"/>
+      <c r="D21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="F21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:7">
+      <c r="A22" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="C22" s="9"/>
+      <c r="D22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="F22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:7">
+      <c r="A23" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="C23" s="9"/>
+      <c r="D23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="F23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:7">
+      <c r="A24" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="C24" s="9"/>
+      <c r="D24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="F24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:7">
+      <c r="A25" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="C25" s="9"/>
+      <c r="D25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="F25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:7">
+      <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="C26" s="9"/>
+      <c r="D26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2" t="s">
+      <c r="F26" s="1"/>
+      <c r="G26" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:7">
+      <c r="A27" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="C27" s="9"/>
+      <c r="D27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2" t="s">
+      <c r="F27" s="1"/>
+      <c r="G27" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:7">
+      <c r="A28" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="C28" s="9"/>
+      <c r="D28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="3" t="s">
+      <c r="F28" s="1"/>
+      <c r="G28" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:7">
+      <c r="A29" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="C29" s="9"/>
+      <c r="D29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="3" t="s">
+      <c r="F29" s="1"/>
+      <c r="G29" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:7">
+      <c r="A30" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="C30" s="9"/>
+      <c r="D30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="3" t="s">
+      <c r="F30" s="1"/>
+      <c r="G30" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="1:7">
+      <c r="A31" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="C31" s="9"/>
+      <c r="D31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" s="6" t="s">
+      <c r="F31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:7">
+      <c r="A32" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="C32" s="1"/>
+      <c r="D32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="3" t="s">
+      <c r="F32" s="1"/>
+      <c r="G32" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:7">
+      <c r="A33" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="C33" s="9"/>
+      <c r="D33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="3" t="s">
+      <c r="F33" s="1"/>
+      <c r="G33" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:7">
+      <c r="A34" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="13">
         <v>10209124250</v>
       </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="C34" s="13"/>
+      <c r="D34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="3" t="s">
+      <c r="F34" s="1"/>
+      <c r="G34" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:7">
+      <c r="A35" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="C35" s="9"/>
+      <c r="D35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:7">
+      <c r="A36" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="2" t="s">
+      <c r="C36" s="9"/>
+      <c r="D36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F36" s="2"/>
-      <c r="G36" s="3" t="s">
+      <c r="F36" s="1"/>
+      <c r="G36" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:7">
+      <c r="A37" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G37" s="7" t="s">
+      <c r="C37" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:7">
+      <c r="A38" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C38" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38" s="7" t="s">
+      <c r="C38" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:7">
+      <c r="A39" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C39" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G39" s="7" t="s">
+      <c r="C39" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+    <row r="40" spans="1:7">
+      <c r="A40" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C40" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40" s="7" t="s">
+      <c r="C40" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+    <row r="41" spans="1:7">
+      <c r="A41" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C41" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G41" s="7" t="s">
+      <c r="C41" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+    <row r="42" spans="1:7">
+      <c r="A42" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C42" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G42" s="7" t="s">
+      <c r="D42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+    <row r="43" spans="1:7">
+      <c r="A43" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G43" s="7" t="s">
+      <c r="D43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" s="6" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+    <row r="44" spans="1:7">
+      <c r="A44" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="C44" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G44" s="7" t="s">
+      <c r="C44" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+    <row r="45" spans="1:7">
+      <c r="A45" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="C45" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G45" s="7" t="s">
+      <c r="C45" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="6" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+    <row r="46" spans="1:7">
+      <c r="A46" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="C46" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G46" s="7" t="s">
+      <c r="C46" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+    <row r="47" spans="1:7">
+      <c r="A47" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G47" s="7" t="s">
+      <c r="D47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" s="6" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+    <row r="48" spans="1:7">
+      <c r="A48" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="C48" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G48" s="3" t="s">
+      <c r="C48" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+    <row r="49" spans="1:7">
+      <c r="A49" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G49" s="7" t="s">
+      <c r="C49" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" s="6" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+    <row r="50" spans="1:7">
+      <c r="A50" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="C50" s="11"/>
-      <c r="D50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G50" s="7" t="s">
+      <c r="C50" s="9"/>
+      <c r="D50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
+    <row r="51" spans="1:7">
+      <c r="A51" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="C51" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G51" s="7" t="s">
+      <c r="C51" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" s="6" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+    <row r="52" spans="1:7">
+      <c r="A52" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="9">
         <v>10211148115</v>
       </c>
-      <c r="C52" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G52" s="7" t="s">
+      <c r="C52" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+    <row r="53" spans="1:7">
+      <c r="A53" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="C53" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G53" s="7" t="s">
+      <c r="C53" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53" s="6" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
+    <row r="54" spans="1:7">
+      <c r="A54" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C54" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G54" s="7" t="s">
+      <c r="C54" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+    <row r="55" spans="1:7">
+      <c r="A55" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="C55" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G55" s="7" t="s">
+      <c r="C55" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G55" s="6" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="1:7">
+      <c r="A56" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C56" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G56" s="7" t="s">
+      <c r="C56" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
+    <row r="57" spans="1:7">
+      <c r="A57" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C57" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G57" s="7" t="s">
+      <c r="C57" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G57" s="6" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+    <row r="58" spans="1:7">
+      <c r="A58" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="C58" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G58" s="7" t="s">
+      <c r="C58" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58" s="6" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+    <row r="59" spans="1:7">
+      <c r="A59" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C59" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G59" s="8" t="s">
+      <c r="C59" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" s="7" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+    <row r="60" spans="1:7">
+      <c r="A60" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="C60" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G60" s="7" t="s">
+      <c r="C60" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+    <row r="61" spans="1:7">
+      <c r="A61" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C61" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G61" s="7" t="s">
+      <c r="C61" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G61" s="6" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
+    <row r="62" spans="1:7">
+      <c r="A62" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C62" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G62" s="7" t="s">
+      <c r="C62" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+    <row r="63" spans="1:7">
+      <c r="A63" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="C63" s="11"/>
-      <c r="D63" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G63" s="7" t="s">
+      <c r="C63" s="9"/>
+      <c r="D63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G63" s="6" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
+    <row r="64" spans="1:7">
+      <c r="A64" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="C64" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G64" s="7" t="s">
+      <c r="C64" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+    <row r="65" spans="1:7">
+      <c r="A65" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="C65" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G65" s="7" t="s">
+      <c r="C65" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65" s="6" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+    <row r="66" spans="1:7">
+      <c r="A66" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="C66" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G66" s="7" t="s">
+      <c r="C66" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+    <row r="67" spans="1:7">
+      <c r="A67" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="C67" s="11"/>
-      <c r="D67" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G67" s="7" t="s">
+      <c r="C67" s="9"/>
+      <c r="D67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G67" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
+    <row r="68" spans="1:7">
+      <c r="A68" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="C68" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G68" s="7" t="s">
+      <c r="C68" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
+    <row r="69" spans="1:7">
+      <c r="A69" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C69" s="11"/>
-      <c r="D69" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G69" s="7" t="s">
+      <c r="C69" s="9"/>
+      <c r="D69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G69" s="6" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
+    <row r="70" spans="1:7">
+      <c r="A70" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="C70" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G70" s="7" t="s">
+      <c r="C70" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G70" s="6" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
+    <row r="71" spans="1:7">
+      <c r="A71" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="C71" s="11"/>
-      <c r="D71" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G71" s="7" t="s">
+      <c r="C71" s="9"/>
+      <c r="D71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G71" s="6" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
+    <row r="72" spans="1:7">
+      <c r="A72" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="C72" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G72" s="7" t="s">
+      <c r="C72" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G72" s="6" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+    <row r="73" spans="1:7">
+      <c r="A73" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="C73" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G73" s="7" t="s">
+      <c r="C73" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G73" s="6" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+    <row r="74" spans="1:7">
+      <c r="A74" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="C74" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G74" s="7" t="s">
+      <c r="C74" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+    <row r="75" spans="1:7">
+      <c r="A75" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="C75" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G75" s="7" t="s">
+      <c r="C75" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G75" s="6" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+    <row r="76" spans="1:7">
+      <c r="A76" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="C76" s="11"/>
-      <c r="D76" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G76" s="7" t="s">
+      <c r="C76" s="9"/>
+      <c r="D76" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G76" s="6" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
+    <row r="77" spans="1:7">
+      <c r="A77" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="C77" s="11"/>
-      <c r="D77" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G77" s="7" t="s">
+      <c r="C77" s="9"/>
+      <c r="D77" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G77" s="6" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
+    <row r="78" spans="1:7">
+      <c r="A78" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="C78" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G78" s="7" t="s">
+      <c r="C78" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
+    <row r="79" spans="1:7">
+      <c r="A79" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="C79" s="11"/>
-      <c r="D79" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G79" s="7" t="s">
+      <c r="C79" s="9"/>
+      <c r="D79" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G79" s="6" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
+    <row r="80" spans="1:7">
+      <c r="A80" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="C80" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G80" s="7" t="s">
+      <c r="C80" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G80" s="6" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
+    <row r="81" spans="1:7">
+      <c r="A81" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="C81" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G81" s="7" t="s">
+      <c r="C81" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G81" s="6" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
+    <row r="82" spans="1:7">
+      <c r="A82" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="C82" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G82" s="7" t="s">
+      <c r="C82" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G82" s="6" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
+    <row r="83" spans="1:7">
+      <c r="A83" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="C83" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G83" s="7" t="s">
+      <c r="C83" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G83" s="6" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
+    <row r="84" spans="1:7">
+      <c r="A84" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C84" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G84" s="7" t="s">
+      <c r="C84" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G84" s="6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
+    <row r="85" spans="1:7">
+      <c r="A85" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="C85" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G85" s="7" t="s">
+      <c r="C85" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G85" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
+    <row r="86" spans="1:7">
+      <c r="A86" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="C86" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G86" s="7" t="s">
+      <c r="C86" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G86" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
+    <row r="87" spans="1:7">
+      <c r="A87" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="C87" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G87" s="7" t="s">
+      <c r="C87" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" s="6" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
+    <row r="88" spans="1:7">
+      <c r="A88" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="C88" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G88" s="7" t="s">
+      <c r="C88" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G88" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
+    <row r="89" spans="1:7">
+      <c r="A89" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C89" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G89" s="7" t="s">
+      <c r="C89" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G89" s="6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
+    <row r="90" spans="1:7">
+      <c r="A90" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="C90" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G90" s="7" t="s">
+      <c r="C90" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G90" s="6" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
+    <row r="91" spans="1:7">
+      <c r="A91" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="C91" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G91" s="7" t="s">
+      <c r="C91" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
+    <row r="92" spans="1:7">
+      <c r="A92" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="C92" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G92" s="7" t="s">
+      <c r="C92" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G92" s="6" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
+    <row r="93" spans="1:7">
+      <c r="A93" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="C93" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G93" s="7" t="s">
+      <c r="C93" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G93" s="6" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
+    <row r="94" spans="1:7">
+      <c r="A94" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C94" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G94" s="7" t="s">
+      <c r="C94" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G94" s="6" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
+    <row r="95" spans="1:7">
+      <c r="A95" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="C95" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G95" s="18" t="s">
+      <c r="C95" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G95" s="16" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
+    <row r="96" spans="1:7">
+      <c r="A96" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="C96" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G96" s="7" t="s">
+      <c r="C96" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G96" s="6" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
+    <row r="97" spans="1:7">
+      <c r="A97" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B97" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="C97" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G97" s="7" t="s">
+      <c r="C97" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G97" s="6" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
+    <row r="98" spans="1:7">
+      <c r="A98" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B98" s="11" t="s">
+      <c r="B98" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="C98" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G98" s="7" t="s">
+      <c r="C98" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G98" s="6" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
+    <row r="99" spans="1:7">
+      <c r="A99" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="C99" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G99" s="7" t="s">
+      <c r="C99" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G99" s="6" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
+    <row r="100" spans="1:7">
+      <c r="A100" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B100" s="11" t="s">
+      <c r="B100" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="C100" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G100" s="7" t="s">
+      <c r="C100" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" s="6" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
+    <row r="101" spans="1:7">
+      <c r="A101" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B101" s="11" t="s">
+      <c r="B101" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="C101" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G101" s="7" t="s">
+      <c r="C101" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G101" s="6" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
+    <row r="102" spans="1:7">
+      <c r="A102" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B102" s="11" t="s">
+      <c r="B102" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="C102" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G102" s="7" t="s">
+      <c r="C102" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G102" s="6" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
+    <row r="103" spans="1:7">
+      <c r="A103" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B103" s="11" t="s">
+      <c r="B103" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="C103" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G103" s="7" t="s">
+      <c r="C103" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G103" s="6" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
+    <row r="104" spans="1:7">
+      <c r="A104" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B104" s="11" t="s">
+      <c r="B104" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="C104" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G104" s="7" t="s">
+      <c r="C104" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G104" s="6" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
+    <row r="105" spans="1:7">
+      <c r="A105" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B105" s="11" t="s">
+      <c r="B105" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="C105" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G105" s="7" t="s">
+      <c r="C105" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G105" s="6" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
+    <row r="106" spans="1:7">
+      <c r="A106" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B106" s="11" t="s">
+      <c r="B106" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="C106" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G106" s="8" t="s">
+      <c r="C106" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G106" s="7" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
+    <row r="107" spans="1:7">
+      <c r="A107" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B107" s="11" t="s">
+      <c r="B107" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="C107" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G107" s="7" t="s">
+      <c r="C107" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G107" s="6" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
+    <row r="108" spans="1:7">
+      <c r="A108" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B108" s="11" t="s">
+      <c r="B108" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="C108" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G108" s="7" t="s">
+      <c r="C108" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G108" s="6" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
+    <row r="109" spans="1:7">
+      <c r="A109" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B109" s="11" t="s">
+      <c r="B109" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="C109" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G109" s="7" t="s">
+      <c r="C109" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G109" s="6" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
+    <row r="110" spans="1:7">
+      <c r="A110" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B110" s="11" t="s">
+      <c r="B110" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="C110" s="11"/>
-      <c r="D110" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G110" s="7" t="s">
+      <c r="C110" s="9"/>
+      <c r="D110" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G110" s="6" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
+    <row r="111" spans="1:7">
+      <c r="A111" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B111" s="11" t="s">
+      <c r="B111" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="C111" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G111" s="7" t="s">
+      <c r="C111" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G111" s="6" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
+    <row r="112" spans="1:7">
+      <c r="A112" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B112" s="11" t="s">
+      <c r="B112" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="C112" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G112" s="7" t="s">
+      <c r="C112" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G112" s="6" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
+    <row r="113" spans="1:7">
+      <c r="A113" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B113" s="11" t="s">
+      <c r="B113" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="C113" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G113" s="7" t="s">
+      <c r="C113" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G113" s="6" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
+    <row r="114" spans="1:7">
+      <c r="A114" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B114" s="11" t="s">
+      <c r="B114" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="C114" s="11"/>
-      <c r="D114" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G114" s="7" t="s">
+      <c r="C114" s="9"/>
+      <c r="D114" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G114" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
+    <row r="115" spans="1:7">
+      <c r="A115" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B115" s="11" t="s">
+      <c r="B115" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="C115" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G115" s="7" t="s">
+      <c r="C115" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" s="6" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
+    <row r="116" spans="1:7">
+      <c r="A116" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B116" s="11" t="s">
+      <c r="B116" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="C116" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G116" s="7" t="s">
+      <c r="C116" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G116" s="6" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
+    <row r="117" spans="1:7">
+      <c r="A117" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B117" s="11" t="s">
+      <c r="B117" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="C117" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G117" s="7" t="s">
+      <c r="C117" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G117" s="6" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
+    <row r="118" spans="1:7">
+      <c r="A118" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B118" s="11" t="s">
+      <c r="B118" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="C118" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G118" s="7" t="s">
+      <c r="C118" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G118" s="6" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
+    <row r="119" spans="1:7">
+      <c r="A119" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B119" s="11" t="s">
+      <c r="B119" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="C119" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G119" s="7" t="s">
+      <c r="C119" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G119" s="6" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
+    <row r="120" spans="1:7">
+      <c r="A120" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B120" s="11" t="s">
+      <c r="B120" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="C120" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G120" s="7" t="s">
+      <c r="C120" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G120" s="6" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
+    <row r="121" spans="1:7">
+      <c r="A121" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B121" s="11" t="s">
+      <c r="B121" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="C121" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G121" s="7" t="s">
+      <c r="C121" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G121" s="6" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
+    <row r="122" spans="1:7">
+      <c r="A122" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B122" s="11" t="s">
+      <c r="B122" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="C122" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G122" s="7" t="s">
+      <c r="C122" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G122" s="6" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
+    <row r="123" spans="1:7">
+      <c r="A123" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B123" s="11" t="s">
+      <c r="B123" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="C123" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G123" s="7" t="s">
+      <c r="C123" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G123" s="6" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="2" t="s">
+    <row r="124" spans="1:7">
+      <c r="A124" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B124" s="11" t="s">
+      <c r="B124" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="C124" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G124" s="7" t="s">
+      <c r="C124" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G124" s="6" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="2" t="s">
+    <row r="125" spans="1:7">
+      <c r="A125" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B125" s="11" t="s">
+      <c r="B125" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="C125" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G125" s="7" t="s">
+      <c r="C125" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G125" s="6" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
+    <row r="126" spans="1:7">
+      <c r="A126" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B126" s="11" t="s">
+      <c r="B126" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="C126" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G126" s="7" t="s">
+      <c r="C126" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G126" s="6" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="2" t="s">
+    <row r="127" spans="1:7">
+      <c r="A127" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B127" s="11" t="s">
+      <c r="B127" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="C127" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G127" s="7" t="s">
+      <c r="C127" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G127" s="6" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="2" t="s">
+    <row r="128" spans="1:7">
+      <c r="A128" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B128" s="11" t="s">
+      <c r="B128" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="C128" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G128" s="7" t="s">
+      <c r="C128" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G128" s="6" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="2" t="s">
+    <row r="129" spans="1:7">
+      <c r="A129" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B129" s="11" t="s">
+      <c r="B129" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="C129" s="11"/>
-      <c r="D129" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G129" s="7" t="s">
+      <c r="C129" s="9"/>
+      <c r="D129" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G129" s="6" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" s="2" t="s">
+    <row r="130" spans="1:7">
+      <c r="A130" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B130" s="11" t="s">
+      <c r="B130" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="C130" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G130" s="7" t="s">
+      <c r="C130" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G130" s="6" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" s="2" t="s">
+    <row r="131" spans="1:7">
+      <c r="A131" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B131" s="11" t="s">
+      <c r="B131" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="C131" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G131" s="7" t="s">
+      <c r="C131" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G131" s="6" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A132" s="3" t="s">
+    <row r="132" spans="1:7">
+      <c r="A132" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B132" s="13" t="s">
+      <c r="B132" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="C132" s="13"/>
-      <c r="D132" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E132" s="2" t="s">
+      <c r="C132" s="11"/>
+      <c r="D132" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" s="3" t="s">
+      <c r="F132" s="1"/>
+      <c r="G132" s="1"/>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B133" s="13" t="s">
+      <c r="B133" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="C133" s="13"/>
-      <c r="D133" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E133" s="2" t="s">
+      <c r="C133" s="11"/>
+      <c r="D133" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A134" s="3" t="s">
+      <c r="F133" s="1"/>
+      <c r="G133" s="1"/>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B134" s="13" t="s">
+      <c r="B134" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="C134" s="13"/>
-      <c r="D134" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E134" s="2" t="s">
+      <c r="C134" s="11"/>
+      <c r="D134" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" s="2" t="s">
+      <c r="F134" s="1"/>
+      <c r="G134" s="1"/>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B135" s="11" t="s">
+      <c r="B135" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="C135" s="11"/>
-      <c r="D135" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E135" s="2" t="s">
+      <c r="C135" s="9"/>
+      <c r="D135" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="F135" s="2" t="s">
+      <c r="F135" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G135" s="2" t="s">
+      <c r="G135" s="1" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A136" s="2" t="s">
+    <row r="136" spans="1:7">
+      <c r="A136" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B136" s="11" t="s">
+      <c r="B136" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="C136" s="11"/>
-      <c r="D136" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E136" s="2" t="s">
+      <c r="C136" s="9"/>
+      <c r="D136" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="F136" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G136" s="2" t="s">
+      <c r="F136" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G136" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137" s="2" t="s">
+    <row r="137" spans="1:7">
+      <c r="A137" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B137" s="11" t="s">
+      <c r="B137" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="C137" s="11"/>
-      <c r="D137" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E137" s="2" t="s">
+      <c r="C137" s="9"/>
+      <c r="D137" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="F137" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G137" s="2" t="s">
+      <c r="F137" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G137" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138" s="2" t="s">
+    <row r="138" spans="1:7">
+      <c r="A138" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B138" s="11" t="s">
+      <c r="B138" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="C138" s="11"/>
-      <c r="D138" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E138" s="2" t="s">
+      <c r="C138" s="9"/>
+      <c r="D138" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="F138" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G138" s="2" t="s">
+      <c r="F138" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G138" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A139" s="2" t="s">
+    <row r="139" spans="1:7">
+      <c r="A139" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B139" s="11" t="s">
+      <c r="B139" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="11"/>
-      <c r="D139" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E139" s="2" t="s">
+      <c r="C139" s="9"/>
+      <c r="D139" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E139" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="F139" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G139" s="2" t="s">
+      <c r="F139" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G139" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A140" s="2" t="s">
+    <row r="140" spans="1:7">
+      <c r="A140" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B140" s="11" t="s">
+      <c r="B140" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="C140" s="11"/>
-      <c r="D140" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E140" s="2" t="s">
+      <c r="C140" s="9"/>
+      <c r="D140" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="F140" s="2"/>
-      <c r="G140" s="2" t="s">
+      <c r="F140" s="1"/>
+      <c r="G140" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A141" s="4" t="s">
+    <row r="141" spans="1:7">
+      <c r="A141" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="B141" s="12"/>
-      <c r="C141" s="12"/>
-      <c r="D141" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E141" s="4" t="s">
+      <c r="B141" s="10"/>
+      <c r="C141" s="10"/>
+      <c r="D141" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E141" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="F141" s="4"/>
-      <c r="G141" s="4"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A142" s="2" t="s">
+      <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B142" s="11" t="s">
+      <c r="B142" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="C142" s="11"/>
-      <c r="D142" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E142" s="2" t="s">
+      <c r="C142" s="9"/>
+      <c r="D142" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="F142" s="2"/>
-      <c r="G142" s="2" t="s">
+      <c r="F142" s="1"/>
+      <c r="G142" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A143" s="2" t="s">
+    <row r="143" spans="1:7">
+      <c r="A143" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B143" s="11" t="s">
+      <c r="B143" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="C143" s="11"/>
-      <c r="D143" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E143" s="2" t="s">
+      <c r="C143" s="9"/>
+      <c r="D143" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="F143" s="2"/>
-      <c r="G143" s="2" t="s">
+      <c r="F143" s="1"/>
+      <c r="G143" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A144" s="4" t="s">
+    <row r="144" spans="1:7">
+      <c r="A144" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="B144" s="12"/>
-      <c r="C144" s="12"/>
-      <c r="D144" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E144" s="4" t="s">
+      <c r="B144" s="10"/>
+      <c r="C144" s="10"/>
+      <c r="D144" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E144" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="F144" s="4"/>
-      <c r="G144" s="4"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145" s="4" t="s">
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="B145" s="12"/>
-      <c r="C145" s="12"/>
-      <c r="D145" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E145" s="4" t="s">
+      <c r="B145" s="10"/>
+      <c r="C145" s="10"/>
+      <c r="D145" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E145" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="F145" s="4"/>
-      <c r="G145" s="4"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A146" s="2" t="s">
+      <c r="F145" s="3"/>
+      <c r="G145" s="3"/>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B146" s="11" t="s">
+      <c r="B146" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="C146" s="11"/>
-      <c r="D146" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E146" s="2" t="s">
+      <c r="C146" s="9"/>
+      <c r="D146" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E146" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="F146" s="2"/>
-      <c r="G146" s="2"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147" s="2" t="s">
+      <c r="F146" s="1"/>
+      <c r="G146" s="1"/>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B147" s="15">
+      <c r="B147" s="13">
         <v>10201132128</v>
       </c>
-      <c r="C147" s="15"/>
-      <c r="D147" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E147" s="2" t="s">
+      <c r="C147" s="13"/>
+      <c r="D147" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="F147" s="2"/>
-      <c r="G147" s="2" t="s">
+      <c r="F147" s="1"/>
+      <c r="G147" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A148" s="2" t="s">
+    <row r="148" spans="1:7">
+      <c r="A148" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B148" s="11">
+      <c r="B148" s="9">
         <v>10201133100</v>
       </c>
-      <c r="C148" s="11"/>
-      <c r="D148" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E148" s="2" t="s">
+      <c r="C148" s="9"/>
+      <c r="D148" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="F148" s="2"/>
-      <c r="G148" s="2" t="s">
+      <c r="F148" s="1"/>
+      <c r="G148" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A149" s="2" t="s">
+    <row r="149" spans="1:7">
+      <c r="A149" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B149" s="11" t="s">
+      <c r="B149" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="C149" s="11"/>
-      <c r="D149" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E149" s="2" t="s">
+      <c r="C149" s="9"/>
+      <c r="D149" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E149" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="F149" s="2"/>
-      <c r="G149" s="2" t="s">
+      <c r="F149" s="1"/>
+      <c r="G149" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A150" s="4" t="s">
+    <row r="150" spans="1:7">
+      <c r="A150" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="B150" s="12"/>
-      <c r="C150" s="12"/>
-      <c r="D150" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E150" s="4" t="s">
+      <c r="B150" s="10"/>
+      <c r="C150" s="10"/>
+      <c r="D150" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E150" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="F150" s="4"/>
-      <c r="G150" s="4"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A151" s="2" t="s">
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B151" s="11" t="s">
+      <c r="B151" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="C151" s="11"/>
-      <c r="D151" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E151" s="2" t="s">
+      <c r="C151" s="9"/>
+      <c r="D151" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E151" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="F151" s="2"/>
-      <c r="G151" s="2"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A152" s="4" t="s">
+      <c r="F151" s="1"/>
+      <c r="G151" s="1"/>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="B152" s="12"/>
-      <c r="C152" s="12"/>
-      <c r="D152" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E152" s="4" t="s">
+      <c r="B152" s="10"/>
+      <c r="C152" s="10"/>
+      <c r="D152" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E152" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="F152" s="4"/>
-      <c r="G152" s="4"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A153" s="2" t="s">
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B153" s="11" t="s">
+      <c r="B153" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="C153" s="11"/>
-      <c r="D153" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E153" s="2" t="s">
+      <c r="C153" s="9"/>
+      <c r="D153" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="F153" s="2"/>
-      <c r="G153" s="2"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A154" s="2" t="s">
+      <c r="F153" s="1"/>
+      <c r="G153" s="1"/>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B154" s="11" t="s">
+      <c r="B154" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="C154" s="11"/>
-      <c r="D154" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E154" s="2" t="s">
+      <c r="C154" s="9"/>
+      <c r="D154" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="F154" s="2"/>
-      <c r="G154" s="2" t="s">
+      <c r="F154" s="1"/>
+      <c r="G154" s="1" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A155" s="2" t="s">
+    <row r="155" spans="1:7">
+      <c r="A155" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B155" s="11" t="s">
+      <c r="B155" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="C155" s="11"/>
-      <c r="D155" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E155" s="2" t="s">
+      <c r="C155" s="9"/>
+      <c r="D155" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="F155" s="2" t="s">
+      <c r="F155" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="G155" s="2" t="s">
+      <c r="G155" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A156" s="2" t="s">
+    <row r="156" spans="1:7">
+      <c r="A156" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B156" s="11" t="s">
+      <c r="B156" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="C156" s="11"/>
-      <c r="D156" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E156" s="2" t="s">
+      <c r="C156" s="9"/>
+      <c r="D156" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E156" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="F156" s="2" t="s">
+      <c r="F156" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="G156" s="2" t="s">
+      <c r="G156" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A157" s="2" t="s">
+    <row r="157" spans="1:7">
+      <c r="A157" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B157" s="11" t="s">
+      <c r="B157" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="C157" s="11"/>
-      <c r="D157" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E157" s="2" t="s">
+      <c r="C157" s="9"/>
+      <c r="D157" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="F157" s="2"/>
-      <c r="G157" s="2" t="s">
+      <c r="F157" s="1"/>
+      <c r="G157" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A158" s="2" t="s">
+    <row r="158" spans="1:7">
+      <c r="A158" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B158" s="11" t="s">
+      <c r="B158" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="C158" s="11"/>
-      <c r="D158" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E158" s="2" t="s">
+      <c r="C158" s="9"/>
+      <c r="D158" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="F158" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G158" s="9" t="s">
+      <c r="F158" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G158" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A159" s="2" t="s">
+    <row r="159" spans="1:7">
+      <c r="A159" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B159" s="11" t="s">
+      <c r="B159" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="C159" s="11"/>
-      <c r="D159" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E159" s="2" t="s">
+      <c r="C159" s="9"/>
+      <c r="D159" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="F159" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G159" s="9" t="s">
+      <c r="F159" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G159" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A160" s="2" t="s">
+    <row r="160" spans="1:7">
+      <c r="A160" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B160" s="11" t="s">
+      <c r="B160" s="9" t="s">
         <v>414</v>
       </c>
-      <c r="C160" s="11"/>
-      <c r="D160" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E160" s="2" t="s">
+      <c r="C160" s="9"/>
+      <c r="D160" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="F160" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G160" s="9" t="s">
+      <c r="F160" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G160" s="8" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A161" s="2" t="s">
+    <row r="161" spans="1:7">
+      <c r="A161" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B161" s="11" t="s">
+      <c r="B161" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="C161" s="11"/>
-      <c r="D161" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E161" s="2" t="s">
+      <c r="C161" s="9"/>
+      <c r="D161" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="F161" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G161" s="9" t="s">
+      <c r="F161" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G161" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A162" s="2" t="s">
+    <row r="162" spans="1:7">
+      <c r="A162" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B162" s="11" t="s">
+      <c r="B162" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="C162" s="11"/>
-      <c r="D162" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E162" s="2" t="s">
+      <c r="C162" s="9"/>
+      <c r="D162" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="F162" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G162" s="9" t="s">
+      <c r="F162" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G162" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A163" s="2" t="s">
+    <row r="163" spans="1:7">
+      <c r="A163" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B163" s="11" t="s">
+      <c r="B163" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="C163" s="11"/>
-      <c r="D163" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E163" s="2" t="s">
+      <c r="C163" s="9"/>
+      <c r="D163" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="F163" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G163" s="9" t="s">
+      <c r="F163" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G163" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A164" s="2" t="s">
+    <row r="164" spans="1:7">
+      <c r="A164" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B164" s="11" t="s">
+      <c r="B164" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="C164" s="11"/>
-      <c r="D164" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E164" s="2" t="s">
+      <c r="C164" s="9"/>
+      <c r="D164" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="F164" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G164" s="9" t="s">
+      <c r="F164" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G164" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A165" s="2" t="s">
+    <row r="165" spans="1:7">
+      <c r="A165" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B165" s="11" t="s">
+      <c r="B165" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="C165" s="11"/>
-      <c r="D165" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E165" s="2" t="s">
+      <c r="C165" s="9"/>
+      <c r="D165" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="F165" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G165" s="9" t="s">
+      <c r="F165" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G165" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A166" s="2" t="s">
+    <row r="166" spans="1:7">
+      <c r="A166" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B166" s="11" t="s">
+      <c r="B166" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="C166" s="11"/>
-      <c r="D166" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E166" s="2" t="s">
+      <c r="C166" s="9"/>
+      <c r="D166" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="F166" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G166" s="9" t="s">
+      <c r="F166" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G166" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A167" s="2" t="s">
+    <row r="167" spans="1:7">
+      <c r="A167" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B167" s="11" t="s">
+      <c r="B167" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="C167" s="11"/>
-      <c r="D167" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E167" s="2" t="s">
+      <c r="C167" s="9"/>
+      <c r="D167" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E167" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="F167" s="2" t="s">
+      <c r="F167" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="G167" s="9" t="s">
+      <c r="G167" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A168" s="2" t="s">
+    <row r="168" spans="1:7">
+      <c r="A168" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B168" s="11" t="s">
+      <c r="B168" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="C168" s="11"/>
-      <c r="D168" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E168" s="2" t="s">
+      <c r="C168" s="9"/>
+      <c r="D168" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E168" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="F168" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G168" s="9" t="s">
+      <c r="F168" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G168" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A169" s="2" t="s">
+    <row r="169" spans="1:7">
+      <c r="A169" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B169" s="11" t="s">
+      <c r="B169" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="C169" s="11"/>
-      <c r="D169" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E169" s="2" t="s">
+      <c r="C169" s="9"/>
+      <c r="D169" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E169" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="F169" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G169" s="9" t="s">
+      <c r="F169" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G169" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A170" s="16" t="s">
+    <row r="170" spans="1:7">
+      <c r="A170" s="14" t="s">
         <v>435</v>
       </c>
-      <c r="B170" s="19"/>
-      <c r="C170" s="19"/>
-      <c r="D170" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E170" s="17" t="s">
+      <c r="B170" s="17"/>
+      <c r="C170" s="17"/>
+      <c r="D170" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E170" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="F170" s="17"/>
-      <c r="G170" s="17"/>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A171" s="16" t="s">
+      <c r="F170" s="15"/>
+      <c r="G170" s="15"/>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" s="14" t="s">
         <v>437</v>
       </c>
-      <c r="B171" s="19"/>
-      <c r="C171" s="19"/>
-      <c r="D171" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E171" s="17" t="s">
+      <c r="B171" s="17"/>
+      <c r="C171" s="17"/>
+      <c r="D171" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E171" s="15" t="s">
         <v>438</v>
       </c>
-      <c r="F171" s="17"/>
-      <c r="G171" s="17"/>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A172" s="2" t="s">
+      <c r="F171" s="15"/>
+      <c r="G171" s="15"/>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B172" s="11" t="s">
+      <c r="B172" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="C172" s="11"/>
-      <c r="D172" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E172" s="2" t="s">
+      <c r="C172" s="9"/>
+      <c r="D172" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E172" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="F172" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G172" s="9" t="s">
+      <c r="F172" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G172" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A173" s="2" t="s">
+    <row r="173" spans="1:7">
+      <c r="A173" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B173" s="11" t="s">
+      <c r="B173" s="9" t="s">
         <v>443</v>
       </c>
-      <c r="C173" s="11"/>
-      <c r="D173" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E173" s="2" t="s">
+      <c r="C173" s="9"/>
+      <c r="D173" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E173" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="F173" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G173" s="2" t="s">
+      <c r="F173" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G173" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A174" s="2" t="s">
+    <row r="174" spans="1:7">
+      <c r="A174" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B174" s="11" t="s">
+      <c r="B174" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="C174" s="11"/>
-      <c r="D174" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E174" s="2" t="s">
+      <c r="C174" s="9"/>
+      <c r="D174" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E174" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="F174" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G174" s="2" t="s">
+      <c r="F174" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G174" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A175" s="2" t="s">
+    <row r="175" spans="1:7">
+      <c r="A175" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B175" s="11" t="s">
+      <c r="B175" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="C175" s="11"/>
-      <c r="D175" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E175" s="2" t="s">
+      <c r="C175" s="9"/>
+      <c r="D175" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E175" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="F175" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G175" s="2" t="s">
+      <c r="F175" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G175" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A176" s="2" t="s">
+    <row r="176" spans="1:7">
+      <c r="A176" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B176" s="11" t="s">
+      <c r="B176" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="C176" s="11"/>
-      <c r="D176" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E176" s="2" t="s">
+      <c r="C176" s="9"/>
+      <c r="D176" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E176" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="F176" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G176" s="2" t="s">
+      <c r="F176" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G176" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A177" s="2" t="s">
+    <row r="177" spans="1:7">
+      <c r="A177" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B177" s="11" t="s">
+      <c r="B177" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="C177" s="11"/>
-      <c r="D177" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E177" s="2" t="s">
+      <c r="C177" s="9"/>
+      <c r="D177" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E177" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="F177" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G177" s="2" t="s">
+      <c r="F177" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G177" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A178" s="2" t="s">
+    <row r="178" spans="1:7">
+      <c r="A178" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B178" s="11" t="s">
+      <c r="B178" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="C178" s="11"/>
-      <c r="D178" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E178" s="2" t="s">
+      <c r="C178" s="9"/>
+      <c r="D178" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="F178" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G178" s="2" t="s">
+      <c r="F178" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G178" s="1" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A179" s="16" t="s">
+    <row r="179" spans="1:7">
+      <c r="A179" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="B179" s="19"/>
-      <c r="C179" s="19"/>
-      <c r="D179" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E179" s="20" t="s">
+      <c r="B179" s="17"/>
+      <c r="C179" s="17"/>
+      <c r="D179" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E179" s="18" t="s">
         <v>458</v>
       </c>
-      <c r="F179" s="20"/>
-      <c r="G179" s="17"/>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A180" s="18" t="s">
+      <c r="F179" s="18"/>
+      <c r="G179" s="15"/>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" s="16" t="s">
         <v>459</v>
       </c>
-      <c r="B180" s="25" t="s">
+      <c r="B180" s="23" t="s">
         <v>460</v>
       </c>
-      <c r="C180" s="25"/>
-      <c r="D180" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E180" s="2" t="s">
+      <c r="C180" s="23"/>
+      <c r="D180" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E180" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="F180" s="2"/>
-      <c r="G180" s="2" t="s">
+      <c r="F180" s="1"/>
+      <c r="G180" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A181" s="2" t="s">
+    <row r="181" spans="1:7">
+      <c r="A181" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B181" s="2" t="s">
+      <c r="B181" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C181" s="2"/>
-      <c r="D181" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E181" s="2"/>
-      <c r="F181" s="2" t="s">
+      <c r="C181" s="1"/>
+      <c r="D181" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E181" s="1"/>
+      <c r="F181" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="G181" s="2" t="s">
+      <c r="G181" s="1" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A182" s="2" t="s">
+    <row r="182" spans="1:7">
+      <c r="A182" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B182" s="11" t="s">
+      <c r="B182" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="C182" s="11"/>
-      <c r="D182" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E182" s="2" t="s">
+      <c r="C182" s="9"/>
+      <c r="D182" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F182" s="2"/>
-      <c r="G182" s="2" t="s">
+      <c r="F182" s="1"/>
+      <c r="G182" s="1" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A183" s="2" t="s">
+    <row r="183" spans="1:7">
+      <c r="A183" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B183" s="2" t="s">
+      <c r="B183" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="C183" s="2"/>
-      <c r="D183" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E183" s="2" t="s">
+      <c r="C183" s="1"/>
+      <c r="D183" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="F183" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G183" s="2" t="s">
+      <c r="F183" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G183" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A184" s="21" t="s">
+    <row r="184" spans="1:7">
+      <c r="A184" s="19" t="s">
         <v>471</v>
       </c>
-      <c r="B184" s="22" t="s">
+      <c r="B184" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="C184" s="22"/>
-      <c r="D184" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="E184" s="23" t="s">
+      <c r="C184" s="20"/>
+      <c r="D184" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E184" s="21" t="s">
         <v>472</v>
       </c>
-      <c r="F184" s="23" t="s">
+      <c r="F184" s="21" t="s">
         <v>472</v>
       </c>
-      <c r="G184" s="23" t="s">
+      <c r="G184" s="21" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A185" s="4" t="s">
+    <row r="185" spans="1:7">
+      <c r="A185" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="B185" s="12"/>
-      <c r="C185" s="12"/>
-      <c r="D185" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E185" s="4"/>
-      <c r="F185" s="4"/>
-      <c r="G185" s="4" t="s">
+      <c r="B185" s="10"/>
+      <c r="C185" s="10"/>
+      <c r="D185" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E185" s="3"/>
+      <c r="F185" s="3"/>
+      <c r="G185" s="3" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A186" s="2" t="s">
+    <row r="186" spans="1:7">
+      <c r="A186" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B186" s="11" t="s">
+      <c r="B186" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="C186" s="11"/>
-      <c r="D186" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E186" s="2" t="s">
+      <c r="C186" s="9"/>
+      <c r="D186" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E186" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="F186" s="2"/>
-      <c r="G186" s="2" t="s">
+      <c r="F186" s="1"/>
+      <c r="G186" s="1" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A187" s="2" t="s">
+    <row r="187" spans="1:7">
+      <c r="A187" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B187" s="11" t="s">
+      <c r="B187" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="C187" s="11"/>
-      <c r="D187" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E187" s="2" t="s">
+      <c r="C187" s="9"/>
+      <c r="D187" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E187" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="F187" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G187" s="2" t="s">
+      <c r="F187" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G187" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A188" s="2" t="s">
+    <row r="188" spans="1:7">
+      <c r="A188" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B188" s="11" t="s">
+      <c r="B188" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="C188" s="11"/>
-      <c r="D188" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E188" s="2"/>
-      <c r="F188" s="2" t="s">
+      <c r="C188" s="9"/>
+      <c r="D188" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E188" s="1"/>
+      <c r="F188" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="G188" s="2" t="s">
+      <c r="G188" s="1" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A189" s="2" t="s">
+    <row r="189" spans="1:7">
+      <c r="A189" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B189" s="11" t="s">
+      <c r="B189" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="C189" s="11"/>
-      <c r="D189" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E189" s="2" t="s">
+      <c r="C189" s="9"/>
+      <c r="D189" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="F189" s="2" t="s">
+      <c r="F189" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="G189" s="2" t="s">
+      <c r="G189" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A190" s="2" t="s">
+    <row r="190" spans="1:7">
+      <c r="A190" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="B190" s="11" t="s">
+      <c r="B190" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="C190" s="11"/>
-      <c r="D190" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E190" s="2" t="s">
+      <c r="C190" s="9"/>
+      <c r="D190" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E190" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="F190" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G190" s="2" t="s">
+      <c r="F190" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G190" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A191" s="26" t="s">
+    <row r="191" spans="1:7">
+      <c r="A191" s="24" t="s">
         <v>491</v>
       </c>
-      <c r="B191" s="27"/>
-      <c r="C191" s="27"/>
-      <c r="D191" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="E191" s="28"/>
-      <c r="F191" s="28"/>
-      <c r="G191" s="28"/>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A192" s="2" t="s">
+      <c r="B191" s="25"/>
+      <c r="C191" s="25"/>
+      <c r="D191" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E191" s="26"/>
+      <c r="F191" s="26"/>
+      <c r="G191" s="26"/>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="B192" s="11" t="s">
+      <c r="B192" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="C192" s="11"/>
-      <c r="D192" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E192" s="2" t="s">
+      <c r="C192" s="9"/>
+      <c r="D192" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E192" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="F192" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G192" s="2" t="s">
+      <c r="F192" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G192" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A193" s="2" t="s">
+    <row r="193" spans="1:7">
+      <c r="A193" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B193" s="11" t="s">
+      <c r="B193" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="C193" s="11"/>
-      <c r="D193" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E193" s="2" t="s">
+      <c r="C193" s="9"/>
+      <c r="D193" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E193" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="F193" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G193" s="2" t="s">
+      <c r="F193" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G193" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A194" s="2" t="s">
+    <row r="194" spans="1:7">
+      <c r="A194" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B194" s="11" t="s">
+      <c r="B194" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="C194" s="11"/>
-      <c r="D194" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E194" s="2" t="s">
+      <c r="C194" s="9"/>
+      <c r="D194" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E194" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="F194" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G194" s="2" t="s">
+      <c r="F194" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G194" s="1" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A195" s="2" t="s">
+    <row r="195" spans="1:7">
+      <c r="A195" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B195" s="11" t="s">
+      <c r="B195" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="C195" s="11"/>
-      <c r="D195" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E195" s="2" t="s">
+      <c r="C195" s="9"/>
+      <c r="D195" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E195" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="F195" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G195" s="2" t="s">
+      <c r="F195" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G195" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A196" s="30" t="s">
+    <row r="196" spans="1:7">
+      <c r="A196" s="28" t="s">
         <v>502</v>
       </c>
-      <c r="B196" s="11" t="s">
+      <c r="B196" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="C196" s="11"/>
-      <c r="D196" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E196" s="2" t="s">
+      <c r="C196" s="9"/>
+      <c r="D196" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F196" s="2"/>
-      <c r="G196" s="2" t="s">
+      <c r="F196" s="1"/>
+      <c r="G196" s="1" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A197" s="2" t="s">
+    <row r="197" spans="1:7">
+      <c r="A197" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B197" s="29" t="s">
+      <c r="B197" s="27" t="s">
         <v>505</v>
       </c>
-      <c r="C197" s="11"/>
-      <c r="D197" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E197" s="2" t="s">
+      <c r="C197" s="9"/>
+      <c r="D197" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="F197" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G197" s="2" t="s">
+      <c r="F197" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G197" s="1" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A198" s="2" t="s">
+    <row r="198" spans="1:7">
+      <c r="A198" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B198" s="29" t="s">
+      <c r="B198" s="27" t="s">
         <v>509</v>
       </c>
-      <c r="C198" s="11"/>
-      <c r="D198" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E198" s="2" t="s">
+      <c r="C198" s="9"/>
+      <c r="D198" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="F198" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G198" s="2" t="s">
+      <c r="F198" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G198" s="1" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A199" s="31" t="s">
+    <row r="199" spans="1:7">
+      <c r="A199" s="29" t="s">
         <v>510</v>
       </c>
-      <c r="B199" s="29" t="s">
+      <c r="B199" s="27" t="s">
         <v>511</v>
       </c>
-      <c r="C199" s="11"/>
-      <c r="D199" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E199" s="2" t="s">
+      <c r="C199" s="9"/>
+      <c r="D199" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="F199" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G199" s="2" t="s">
+      <c r="F199" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G199" s="1" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A200" s="2" t="s">
+    <row r="200" spans="1:7">
+      <c r="A200" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B200" s="11" t="s">
+      <c r="B200" s="9" t="s">
         <v>513</v>
       </c>
-      <c r="C200" s="11"/>
-      <c r="D200" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E200" s="2" t="s">
+      <c r="C200" s="9"/>
+      <c r="D200" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E200" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="F200" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G200" s="2" t="s">
+      <c r="F200" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G200" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A201" s="2" t="s">
+    <row r="201" spans="1:7">
+      <c r="A201" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B201" s="11" t="s">
+      <c r="B201" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="C201" s="11"/>
-      <c r="D201" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E201" s="2" t="s">
+      <c r="C201" s="9"/>
+      <c r="D201" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="F201" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G201" s="2" t="s">
+      <c r="F201" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G201" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A202" s="2" t="s">
+    <row r="202" spans="1:7">
+      <c r="A202" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="B202" s="11" t="s">
+      <c r="B202" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="C202" s="11"/>
-      <c r="D202" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E202" s="2" t="s">
+      <c r="C202" s="9"/>
+      <c r="D202" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E202" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="F202" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G202" s="2" t="s">
+      <c r="F202" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G202" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A203" s="4" t="s">
+    <row r="203" spans="1:7">
+      <c r="A203" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="B203" s="12" t="s">
+      <c r="B203" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="C203" s="12"/>
-      <c r="D203" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E203" s="4"/>
-      <c r="F203" s="4"/>
-      <c r="G203" s="4"/>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A204" s="2" t="s">
+      <c r="C203" s="10"/>
+      <c r="D203" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E203" s="3"/>
+      <c r="F203" s="3"/>
+      <c r="G203" s="3"/>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="B204" s="11" t="s">
+      <c r="B204" s="9" t="s">
         <v>522</v>
       </c>
-      <c r="C204" s="11"/>
-      <c r="D204" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E204" s="2" t="s">
+      <c r="C204" s="9"/>
+      <c r="D204" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E204" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="F204" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G204" s="2" t="s">
+      <c r="F204" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G204" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A205" s="32" t="s">
+    <row r="205" spans="1:7">
+      <c r="A205" s="30" t="s">
         <v>523</v>
       </c>
-      <c r="B205" s="33" t="s">
+      <c r="B205" s="31" t="s">
         <v>524</v>
       </c>
-      <c r="C205" s="33" t="s">
+      <c r="C205" s="31" t="s">
         <v>524</v>
       </c>
-      <c r="D205" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="E205" s="32"/>
-      <c r="F205" s="32" t="s">
+      <c r="D205" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E205" s="30"/>
+      <c r="F205" s="30" t="s">
         <v>524</v>
       </c>
-      <c r="G205" s="32" t="s">
+      <c r="G205" s="30" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A206" s="32" t="s">
+    <row r="206" spans="1:7">
+      <c r="A206" s="30" t="s">
         <v>525</v>
       </c>
-      <c r="B206" s="33" t="s">
+      <c r="B206" s="31" t="s">
         <v>524</v>
       </c>
-      <c r="C206" s="33" t="s">
+      <c r="C206" s="31" t="s">
         <v>524</v>
       </c>
-      <c r="D206" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="E206" s="32"/>
-      <c r="F206" s="32" t="s">
+      <c r="D206" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E206" s="30"/>
+      <c r="F206" s="30" t="s">
         <v>524</v>
       </c>
-      <c r="G206" s="32" t="s">
+      <c r="G206" s="30" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A207" s="2" t="s">
+    <row r="207" spans="1:7">
+      <c r="A207" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="B207" s="11" t="s">
+      <c r="B207" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="C207" s="11"/>
-      <c r="D207" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E207" s="2" t="s">
+      <c r="C207" s="9"/>
+      <c r="D207" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E207" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="F207" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G207" s="2" t="s">
+      <c r="F207" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G207" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A208" s="2" t="s">
+    <row r="208" spans="1:7">
+      <c r="A208" s="1" t="s">
         <v>529</v>
       </c>
       <c r="B208" t="s">
         <v>530</v>
       </c>
-      <c r="C208" s="11"/>
-      <c r="D208" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E208" s="2" t="s">
+      <c r="C208" s="9"/>
+      <c r="D208" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="F208" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G208" s="2" t="s">
+      <c r="F208" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G208" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A209" s="2" t="s">
+    <row r="209" spans="1:7">
+      <c r="A209" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="B209" s="2" t="s">
+      <c r="B209" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="C209" s="2"/>
-      <c r="D209" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E209" s="2" t="s">
+      <c r="C209" s="1"/>
+      <c r="D209" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E209" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="F209" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G209" s="2" t="s">
+      <c r="F209" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G209" s="1" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A210" s="2" t="s">
+    <row r="210" spans="1:7">
+      <c r="A210" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="B210" s="11" t="s">
+      <c r="B210" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="C210" s="11"/>
-      <c r="D210" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E210" s="2" t="s">
+      <c r="C210" s="9"/>
+      <c r="D210" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E210" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="F210" s="2" t="s">
+      <c r="F210" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="G210" s="2" t="s">
+      <c r="G210" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A211" s="2" t="s">
+    <row r="211" spans="1:7">
+      <c r="A211" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="B211" s="11" t="s">
+      <c r="B211" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="C211" s="11"/>
-      <c r="D211" s="2" t="s">
+      <c r="C211" s="9"/>
+      <c r="D211" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E211" t="s">
         <v>541</v>
       </c>
-      <c r="F211" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G211" s="2" t="s">
+      <c r="F211" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G211" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A212" s="2" t="s">
+    <row r="212" spans="1:7">
+      <c r="A212" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B212" s="11" t="s">
+      <c r="B212" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="C212" s="11"/>
-      <c r="D212" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E212" s="2"/>
-      <c r="F212" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G212" s="2" t="s">
+      <c r="C212" s="9"/>
+      <c r="D212" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E212" s="1"/>
+      <c r="F212" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G212" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A213" s="2" t="s">
+    <row r="213" spans="1:7">
+      <c r="A213" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="B213" s="11" t="s">
+      <c r="B213" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="C213" s="11"/>
-      <c r="D213" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E213" s="2" t="s">
+      <c r="C213" s="9"/>
+      <c r="D213" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E213" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="F213" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G213" s="2" t="s">
+      <c r="F213" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G213" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A214" s="2" t="s">
+    <row r="214" spans="1:7">
+      <c r="A214" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B214" s="11" t="s">
+      <c r="B214" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="C214" s="11"/>
-      <c r="D214" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E214" s="2" t="s">
+      <c r="C214" s="9"/>
+      <c r="D214" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E214" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="F214" s="2" t="s">
+      <c r="F214" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="G214" s="2" t="s">
+      <c r="G214" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A215" s="2" t="s">
+    <row r="215" spans="1:7">
+      <c r="A215" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B215" s="11" t="s">
+      <c r="B215" s="9" t="s">
         <v>556</v>
       </c>
-      <c r="C215" s="11" t="s">
+      <c r="C215" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D215" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E215" s="2" t="s">
+      <c r="D215" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E215" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="F215" s="2" t="s">
+      <c r="F215" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="G215" s="2" t="s">
+      <c r="G215" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A216" s="2" t="s">
+    <row r="216" spans="1:7">
+      <c r="A216" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B216" s="11" t="s">
+      <c r="B216" s="9" t="s">
         <v>557</v>
       </c>
-      <c r="C216" s="11" t="s">
+      <c r="C216" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D216" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E216" s="2" t="s">
+      <c r="D216" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E216" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="F216" s="2" t="s">
+      <c r="F216" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="G216" s="2" t="s">
+      <c r="G216" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A217" s="2" t="s">
+    <row r="217" spans="1:7">
+      <c r="A217" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="B217" s="11" t="s">
+      <c r="B217" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="C217" s="11" t="s">
+      <c r="C217" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D217" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E217" s="2" t="s">
+      <c r="D217" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E217" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="F217" s="2" t="s">
+      <c r="F217" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="G217" s="2" t="s">
+      <c r="G217" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A218" s="2" t="s">
+    <row r="218" spans="1:7">
+      <c r="A218" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B218" s="11" t="s">
+      <c r="B218" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="C218" s="11" t="s">
+      <c r="C218" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D218" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E218" s="2" t="s">
+      <c r="D218" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E218" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="F218" s="2" t="s">
+      <c r="F218" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="G218" s="2" t="s">
+      <c r="G218" s="1" t="s">
         <v>61</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="VMware">
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="VMware">
       <formula>NOT(ISERROR(SEARCH("VMware",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="RDP">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="RDP">
       <formula>NOT(ISERROR(SEARCH("RDP",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="PAM">
+    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="PAM">
       <formula>NOT(ISERROR(SEARCH("PAM",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="expression" dxfId="1" priority="4">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>(#REF!="FORMATEADO")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="6" priority="6">
       <formula>(#REF!="RETIRADO")</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>